--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>## 1. Знакомство с R</t>
   </si>
@@ -49,15 +49,6 @@
   </si>
   <si>
     <t xml:space="preserve">## 9. Литературное программирование </t>
-  </si>
-  <si>
-    <t>1.09?</t>
-  </si>
-  <si>
-    <t>4.09?</t>
-  </si>
-  <si>
-    <t>15.09?</t>
   </si>
 </sst>
 </file>
@@ -93,11 +84,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -113,9 +105,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -153,7 +145,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -225,7 +217,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -375,79 +367,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>20.09</v>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1" s="1">
+        <v>46284</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>26.09</v>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>46291</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>46298</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>46305</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
+        <v>46312</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
+        <v>46319</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
+        <v>46326</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
+        <v>46333</v>
+      </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>46340</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>9</v>
       </c>

--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,10 +45,10 @@
     <t>## 8. Дискриминантный анализ</t>
   </si>
   <si>
-    <t>## 8. Ординация и классификация с использованием мер сходства-различия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">## 9. Литературное программирование </t>
+    <t>## 9. Ординация и классификация с использованием мер сходства-различия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">## 10. Литературное программирование </t>
   </si>
 </sst>
 </file>
@@ -444,7 +444,9 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>46347</v>
+      </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
